--- a/frontend/public/templates/sample_passage_upload.xlsx
+++ b/frontend/public/templates/sample_passage_upload.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,8 +55,13 @@
         <bgColor rgb="00f96331"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF96331"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -67,16 +83,55 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,600 +497,620 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Question Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Subject Code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Exam Level Code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Passage Paragraph</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Question Text</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Option 1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Correct Option</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Answer Explanation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>COMPREHENSION</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Artificial intelligence is transforming industries across the globe, enhancing productivity and creating new paradigms for problem-solving.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>According to the passage, what is AI doing to industries?</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Destroying them completely</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Transforming them across the globe</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Keeping them unchanged</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Replacing human resources entirely</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>The passage explicitly states that AI is transforming industries across the globe.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>ENGLISH</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="D3" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>The rapid growth of e-commerce has led to significant shifts in consumer behavior, forcing traditional retail stores to adapt or face closure.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>What has forced traditional retail stores to adapt?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Government regulations</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Lack of inventory</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>The rapid growth of e-commerce</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>High taxes</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="K3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>The passage mentions that the rapid growth of e-commerce has led to shifts forcing retail stores to adapt.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>A company observed that its productivity increased by 20% after implementing a four-day workweek, while operating costs decreased by 15%.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>What was the effect on operating costs according to the data?</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Increased by 20%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Decreased by 15%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Remained the same</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Increased by 15%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>The text clearly states that operating costs decreased by 15%.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>DATA_INTERPRETATION_ANALYTICS</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Cloud computing allows businesses to scale resources on demand, reducing the need for upfront hardware investments and providing flexibility.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>What is one major benefit of cloud computing mentioned?</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Reducing the need for upfront hardware investments</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Increasing internet speed</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Replacing all software developers</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Making hardware free</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="K5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>The passage states it reduces the need for upfront hardware investments.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>COMPREHENSION</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Renewable energy sources such as solar and wind power are becoming increasingly cost-competitive with fossil fuels, driving a global transition towards sustainable energy.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>What is driving the global transition towards sustainable energy?</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Depletion of all fossil fuels</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Government mandates only</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Cost-competitiveness of renewable sources</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Lack of alternative options</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>The text explains that the cost-competitiveness of solar and wind power is driving the transition.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>ENGLISH</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="D7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Effective communication in the workplace fosters collaboration, prevents misunderstandings, and significantly boosts overall team morale.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Which of the following is NOT mentioned as a benefit of effective communication?</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Fosters collaboration</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Boosts overall team morale</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Prevents misunderstandings</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Guarantees a salary increase</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>Salary increase is never mentioned in the passage as a benefit of effective communication.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>INDUSTRY_AWARENESS</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="D8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>The automotive industry is currently undergoing a massive shift towards electric vehicles (EVs), driven by environmental concerns and government regulations.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>What is driving the shift towards electric vehicles?</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Lack of gasoline</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Environmental concerns and government regulations</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Consumer demand for faster cars</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>A decrease in battery prices</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>The passage specifies environmental concerns and government regulations as the drivers.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>GRAMMAR</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="D9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>While reading the intricate manual, she discovered that the machine required regular maintenance to function optimally.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>In the context of the sentence, what does the machine require?</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>To be replaced immediately</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>To be ignored</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>Regular maintenance</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>A new operator</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="K9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>The sentence states she discovered the machine required regular maintenance.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>BRAND_AWARENESS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="D10" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>A strong brand identity not only helps a company stand out in a crowded market but also builds trust and loyalty among its customer base.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>What does a strong brand identity build among customers?</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Confusion and doubt</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Trust and loyalty</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>Indifference</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>Anger</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="K10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>The passage explicitly notes that it builds trust and loyalty among the customer base.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>COMPREHENSION</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="D11" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Time management is a critical skill for remote workers, as the lack of a structured office environment can lead to distractions and decreased productivity.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Why is time management critical for remote workers?</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Because they work fewer hours</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Because their bosses can not see them</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Because the lack of a structured environment can lead to distractions</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>Because office environments are always perfectly quiet</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="K11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>The text explains that the lack of structure can lead to distractions, making time management critical.</t>
         </is>
